--- a/out/final/car_main_table.xlsx
+++ b/out/final/car_main_table.xlsx
@@ -871,46 +871,46 @@
         <v>26</v>
       </c>
       <c r="E8">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F8">
-        <v>-0.001440157067084521</v>
+        <v>-0.001521740141105669</v>
       </c>
       <c r="G8">
-        <v>0.0006327093043352328</v>
+        <v>0.001086873335108707</v>
       </c>
       <c r="H8">
-        <v>0.04063495841895332</v>
+        <v>0.03957239643563187</v>
       </c>
       <c r="I8">
-        <v>-0.3978279691551084</v>
+        <v>-0.4282121524238586</v>
       </c>
       <c r="J8">
-        <v>0.6914355904355908</v>
+        <v>0.6692455585587206</v>
       </c>
       <c r="K8">
-        <v>3830</v>
+        <v>3833</v>
       </c>
       <c r="L8">
-        <v>0.678040363574274</v>
+        <v>0.9165863311402348</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0.7877465824023323</v>
       </c>
       <c r="N8">
-        <v>0.5</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="O8">
-        <v>-0.104449111287138</v>
+        <v>-0.1641781035903104</v>
       </c>
       <c r="P8">
-        <v>-0.01992803157325626</v>
+        <v>-0.02117889197223996</v>
       </c>
       <c r="Q8">
-        <v>0.0006327093043352328</v>
+        <v>0.001086873335108707</v>
       </c>
       <c r="R8">
-        <v>0.02130740091805133</v>
+        <v>0.01923142064753205</v>
       </c>
       <c r="S8">
         <v>0.08239107533804257</v>
@@ -930,46 +930,46 @@
         <v>27</v>
       </c>
       <c r="E9">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F9">
-        <v>-0.001275812179351532</v>
+        <v>0.003078332807382322</v>
       </c>
       <c r="G9">
-        <v>0.006022233712789427</v>
+        <v>0.006069789060602293</v>
       </c>
       <c r="H9">
-        <v>0.06380211812530646</v>
+        <v>0.05816848737521108</v>
       </c>
       <c r="I9">
-        <v>-0.2244589461261193</v>
+        <v>0.58930298776096</v>
       </c>
       <c r="J9">
-        <v>0.8227666954595833</v>
+        <v>0.5567388799256435</v>
       </c>
       <c r="K9">
-        <v>3810</v>
+        <v>3573</v>
       </c>
       <c r="L9">
-        <v>0.6427657272712657</v>
+        <v>0.4513944349812031</v>
       </c>
       <c r="M9">
-        <v>0.4227911341458804</v>
+        <v>0.5297694043652676</v>
       </c>
       <c r="N9">
-        <v>0.5396825396825397</v>
+        <v>0.532258064516129</v>
       </c>
       <c r="O9">
-        <v>-0.2596941469973632</v>
+        <v>-0.1539596832972503</v>
       </c>
       <c r="P9">
-        <v>-0.03981115931081314</v>
+        <v>-0.02933116236043898</v>
       </c>
       <c r="Q9">
-        <v>0.006022233712789427</v>
+        <v>0.006069789060602293</v>
       </c>
       <c r="R9">
-        <v>0.03756499022782084</v>
+        <v>0.04138451560388978</v>
       </c>
       <c r="S9">
         <v>0.1285087530406699</v>
@@ -989,49 +989,49 @@
         <v>28</v>
       </c>
       <c r="E10">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F10">
-        <v>0.01113217279169253</v>
+        <v>0.01076794548160344</v>
       </c>
       <c r="G10">
-        <v>0.01361053099084081</v>
+        <v>0.01049140121263298</v>
       </c>
       <c r="H10">
-        <v>0.06123262896050644</v>
+        <v>0.06138061594488849</v>
       </c>
       <c r="I10">
-        <v>2.040714759303179</v>
+        <v>1.953495649740572</v>
       </c>
       <c r="J10">
-        <v>0.04338497129970329</v>
+        <v>0.05303118727037582</v>
       </c>
       <c r="K10">
-        <v>3268</v>
+        <v>3017</v>
       </c>
       <c r="L10">
-        <v>0.07450270195839315</v>
+        <v>0.03238870921171225</v>
       </c>
       <c r="M10">
-        <v>0.06093825261566016</v>
+        <v>0.0588758732807349</v>
       </c>
       <c r="N10">
-        <v>0.5873015873015873</v>
+        <v>0.5887096774193549</v>
       </c>
       <c r="O10">
-        <v>-0.1212933711424545</v>
+        <v>-0.1602402713514575</v>
       </c>
       <c r="P10">
-        <v>-0.03655730689081713</v>
+        <v>-0.02929123781457482</v>
       </c>
       <c r="Q10">
-        <v>0.01361053099084081</v>
+        <v>0.01049140121263298</v>
       </c>
       <c r="R10">
-        <v>0.05148064228599952</v>
+        <v>0.05177454922251312</v>
       </c>
       <c r="S10">
-        <v>0.136989278022573</v>
+        <v>0.1328974238733034</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -1048,49 +1048,49 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F11">
-        <v>-0.005071475278376844</v>
+        <v>-0.002366800101149718</v>
       </c>
       <c r="G11">
-        <v>0.0001666784431317847</v>
+        <v>0.0004534339472558324</v>
       </c>
       <c r="H11">
-        <v>0.03110153571378085</v>
+        <v>0.03255642500532013</v>
       </c>
       <c r="I11">
-        <v>-1.830365205609974</v>
+        <v>-0.8095351535047522</v>
       </c>
       <c r="J11">
-        <v>0.06957756818309421</v>
+        <v>0.4197706827375777</v>
       </c>
       <c r="K11">
-        <v>3705</v>
+        <v>3704</v>
       </c>
       <c r="L11">
-        <v>0.4718374589059187</v>
+        <v>0.669801956146495</v>
       </c>
       <c r="M11">
-        <v>0.9290596866317961</v>
+        <v>0.7877465824023323</v>
       </c>
       <c r="N11">
-        <v>0.5079365079365079</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="O11">
-        <v>-0.08839193461339623</v>
+        <v>-0.1392728518307003</v>
       </c>
       <c r="P11">
-        <v>-0.01570313169230553</v>
+        <v>-0.01557463188003827</v>
       </c>
       <c r="Q11">
-        <v>0.0001666784431317847</v>
+        <v>0.0004534339472558324</v>
       </c>
       <c r="R11">
-        <v>0.01680736764973989</v>
+        <v>0.01194305137901588</v>
       </c>
       <c r="S11">
-        <v>0.0703273210946509</v>
+        <v>0.09744494703969608</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -1107,49 +1107,49 @@
         <v>30</v>
       </c>
       <c r="E12">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F12">
-        <v>-0.005316255121843781</v>
+        <v>0.002026827195601676</v>
       </c>
       <c r="G12">
-        <v>-0.002699282127191227</v>
+        <v>0.003614655807093248</v>
       </c>
       <c r="H12">
-        <v>0.04445751403069972</v>
+        <v>0.04460725478822427</v>
       </c>
       <c r="I12">
-        <v>-1.342288633112883</v>
+        <v>0.5059668559682267</v>
       </c>
       <c r="J12">
-        <v>0.1819352503580759</v>
+        <v>0.6137855334210134</v>
       </c>
       <c r="K12">
-        <v>3687</v>
+        <v>3638</v>
       </c>
       <c r="L12">
-        <v>0.4452728381954807</v>
+        <v>0.5545184652607543</v>
       </c>
       <c r="M12">
-        <v>0.7893959446881439</v>
+        <v>0.3232476471849839</v>
       </c>
       <c r="N12">
-        <v>0.4841269841269841</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="O12">
-        <v>-0.2265968199888795</v>
+        <v>-0.1101247554184753</v>
       </c>
       <c r="P12">
-        <v>-0.03146135434877073</v>
+        <v>-0.02549269245060712</v>
       </c>
       <c r="Q12">
-        <v>-0.002699282127191227</v>
+        <v>0.003614655807093248</v>
       </c>
       <c r="R12">
-        <v>0.02272346844321674</v>
+        <v>0.03026763322730511</v>
       </c>
       <c r="S12">
-        <v>0.06562873244499468</v>
+        <v>0.1498206032170635</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -1166,49 +1166,49 @@
         <v>31</v>
       </c>
       <c r="E13">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F13">
-        <v>0.004838882492950836</v>
+        <v>0.00665532325945359</v>
       </c>
       <c r="G13">
-        <v>0.009381557661471585</v>
+        <v>0.008298924930034091</v>
       </c>
       <c r="H13">
-        <v>0.04880083938951085</v>
+        <v>0.05618052125865079</v>
       </c>
       <c r="I13">
-        <v>1.11302022567498</v>
+        <v>1.319150155140065</v>
       </c>
       <c r="J13">
-        <v>0.267835559871506</v>
+        <v>0.1895694166439328</v>
       </c>
       <c r="K13">
-        <v>3503</v>
+        <v>3307</v>
       </c>
       <c r="L13">
-        <v>0.2257695331003672</v>
+        <v>0.1566548953943388</v>
       </c>
       <c r="M13">
-        <v>0.01581820400805213</v>
+        <v>0.02437017012239948</v>
       </c>
       <c r="N13">
-        <v>0.6111111111111112</v>
+        <v>0.6048387096774194</v>
       </c>
       <c r="O13">
         <v>-0.1277418931541138</v>
       </c>
       <c r="P13">
-        <v>-0.027357589469307</v>
+        <v>-0.02856812776015152</v>
       </c>
       <c r="Q13">
-        <v>0.009381557661471585</v>
+        <v>0.008298924930034091</v>
       </c>
       <c r="R13">
-        <v>0.03242195276584961</v>
+        <v>0.0371319064615849</v>
       </c>
       <c r="S13">
-        <v>0.1247141333426937</v>
+        <v>0.138151985855692</v>
       </c>
     </row>
     <row r="14" spans="1:19">
